--- a/02_DIA_inicio_2026_analisis_assets/rbd_9426_escuela-llano-subercaseaux_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9426_escuela-llano-subercaseaux_nt2_rubricas.xlsx
@@ -1932,13 +1932,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C42A894C-D8D9-4E26-A27D-2FD899BDC44E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF2F17A-BCAF-4519-9C8C-1522811B2A6F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F68CE67E-A040-4D30-89F2-22B4477BBF02}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0E9634A-0720-43F5-B32D-CBAF284AB540}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76C965AF-0691-4525-8BA6-9D601470D459}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2BEBDA9-5BC6-4704-81A3-33E7DA3165A4}"/>
 </file>